--- a/assignment3/data/trainingdataset_ontario_budgets_v12_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v12_llm_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA083AB-7BBF-424D-BE4B-4A5B81D878BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0FEFC6-7E3C-EC4E-BD5C-BA9DBBEAF41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="840" windowWidth="36440" windowHeight="20100" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="440" yWindow="500" windowWidth="36440" windowHeight="20100" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
